--- a/output.xlsx
+++ b/output.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Петренко В.Г.</t>
+          <t>Петров А.Б.</t>
         </is>
       </c>
     </row>
@@ -433,42 +433,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Петрин Д.Е.</t>
+          <t>Петренко В.Г.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Петров А.Б.</t>
+          <t>Петрин Д.Е.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Иваньчевич Н.Р.</t>
+          <t>Иваньченко Й.К.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Иванов З.И.</t>
+          <t>Иваньчук Л.М.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Иваньченко Й.К.</t>
+          <t>Иванов З.И.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Иваньчук Л.М.</t>
+          <t>Иваньчевич Н.Р.</t>
         </is>
       </c>
     </row>
